--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-05-06T15:27:29.393Z</t>
+    <t>2026-05-06T17:35:08.231Z</t>
   </si>
   <si>
     <t>DXC Technology | Impossible Delivered | Enterprise Technology &amp; Innovation Solutions</t>
